--- a/Team-Data/2013-14/3-30-2013-14.xlsx
+++ b/Team-Data/2013-14/3-30-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -763,7 +830,7 @@
         <v>12</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
@@ -781,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -793,10 +860,10 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>25</v>
@@ -805,13 +872,13 @@
         <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>0.315</v>
+        <v>0.319</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
         <v>83.90000000000001</v>
@@ -870,13 +937,13 @@
         <v>6.7</v>
       </c>
       <c r="M3" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N3" t="n">
         <v>0.331</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P3" t="n">
         <v>21</v>
@@ -888,10 +955,10 @@
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U3" t="n">
         <v>20.8</v>
@@ -912,16 +979,16 @@
         <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>-4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -954,7 +1021,7 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -969,7 +1036,7 @@
         <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
         <v>25</v>
@@ -984,7 +1051,7 @@
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -993,10 +1060,10 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -1025,55 +1092,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="n">
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.542</v>
+        <v>0.535</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L4" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M4" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="N4" t="n">
         <v>0.372</v>
       </c>
       <c r="O4" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R4" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S4" t="n">
         <v>29.5</v>
       </c>
       <c r="T4" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="U4" t="n">
         <v>20.8</v>
@@ -1082,7 +1149,7 @@
         <v>14.3</v>
       </c>
       <c r="W4" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X4" t="n">
         <v>3.9</v>
@@ -1097,13 +1164,13 @@
         <v>20.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1145,7 +1212,7 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1154,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1172,10 +1239,10 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>16</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1315,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
         <v>14</v>
@@ -1336,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -1389,55 +1456,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J6" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.43</v>
+        <v>0.428</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0.775</v>
       </c>
       <c r="R6" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="S6" t="n">
         <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U6" t="n">
         <v>22.3</v>
@@ -1452,22 +1519,22 @@
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="AC6" t="n">
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1503,16 +1570,16 @@
         <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
         <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>0.392</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
@@ -1589,16 +1656,16 @@
         <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.433</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
         <v>0.358</v>
@@ -1610,13 +1677,13 @@
         <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R7" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
         <v>44.1</v>
@@ -1634,7 +1701,7 @@
         <v>3.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
@@ -1643,10 +1710,10 @@
         <v>19.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.1</v>
+        <v>-4.3</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -1700,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -1724,7 +1791,7 @@
         <v>22</v>
       </c>
       <c r="BC7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1879,13 +1946,13 @@
         <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2025,10 +2092,10 @@
         <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>5</v>
@@ -2037,7 +2104,7 @@
         <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2058,7 +2125,7 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
         <v>3</v>
@@ -2076,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,10 +2274,10 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2243,7 +2310,7 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>21</v>
@@ -2258,13 +2325,13 @@
         <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
         <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>0.616</v>
+        <v>0.625</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J11" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L11" t="n">
         <v>9.1</v>
@@ -2329,16 +2396,16 @@
         <v>24.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O11" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P11" t="n">
         <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R11" t="n">
         <v>11</v>
@@ -2350,13 +2417,13 @@
         <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V11" t="n">
         <v>15.3</v>
       </c>
       <c r="W11" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X11" t="n">
         <v>5.2</v>
@@ -2365,25 +2432,25 @@
         <v>4.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA11" t="n">
         <v>19.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.2</v>
+        <v>103.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
         <v>8</v>
@@ -2392,13 +2459,13 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>7</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>8</v>
-      </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2407,7 +2474,7 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
@@ -2419,7 +2486,7 @@
         <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2428,16 +2495,16 @@
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
         <v>22</v>
       </c>
       <c r="AW11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>5.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2592,7 +2659,7 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2607,7 +2674,7 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" t="n">
         <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.703</v>
+        <v>0.712</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J13" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L13" t="n">
         <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N13" t="n">
         <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P13" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R13" t="n">
         <v>10.3</v>
@@ -2711,7 +2778,7 @@
         <v>34.9</v>
       </c>
       <c r="T13" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U13" t="n">
         <v>20</v>
@@ -2723,10 +2790,10 @@
         <v>6.9</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z13" t="n">
         <v>20.3</v>
@@ -2735,13 +2802,13 @@
         <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2753,7 +2820,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
@@ -2762,7 +2829,7 @@
         <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
         <v>24</v>
@@ -2777,10 +2844,10 @@
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
@@ -2789,10 +2856,10 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
         <v>20</v>
@@ -2804,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
         <v>13</v>
@@ -2816,7 +2883,7 @@
         <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -2923,25 +2990,25 @@
         <v>7.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2968,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -3027,52 +3094,52 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
         <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>0.342</v>
+        <v>0.333</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J15" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M15" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O15" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P15" t="n">
         <v>22.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T15" t="n">
         <v>41.1</v>
@@ -3090,7 +3157,7 @@
         <v>5.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
         <v>20.2</v>
@@ -3099,31 +3166,31 @@
         <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF15" t="n">
         <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
         <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
         <v>14</v>
@@ -3135,7 +3202,7 @@
         <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
@@ -3159,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3168,13 +3235,13 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="n">
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>0.589</v>
+        <v>0.597</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,7 +3294,7 @@
         <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.463</v>
@@ -3236,43 +3303,43 @@
         <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
         <v>15.1</v>
       </c>
       <c r="P16" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R16" t="n">
         <v>11.4</v>
       </c>
       <c r="S16" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T16" t="n">
         <v>42.3</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V16" t="n">
         <v>13.6</v>
       </c>
       <c r="W16" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z16" t="n">
         <v>19.3</v>
@@ -3284,10 +3351,10 @@
         <v>95.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3296,7 +3363,7 @@
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
@@ -3308,7 +3375,7 @@
         <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>30</v>
@@ -3326,13 +3393,13 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>20</v>
@@ -3344,10 +3411,10 @@
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3359,7 +3426,7 @@
         <v>29</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
       </c>
       <c r="AF17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG17" t="n">
         <v>5</v>
@@ -3484,7 +3551,7 @@
         <v>11</v>
       </c>
       <c r="AI17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3496,16 +3563,16 @@
         <v>16</v>
       </c>
       <c r="AM17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
         <v>15</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
@@ -3529,7 +3596,7 @@
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,13 +3605,13 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" t="n">
         <v>36</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3782,7 +3849,7 @@
         <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N19" t="n">
         <v>0.344</v>
@@ -3794,13 +3861,13 @@
         <v>27.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R19" t="n">
         <v>12.6</v>
       </c>
       <c r="S19" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T19" t="n">
         <v>44.9</v>
@@ -3809,13 +3876,13 @@
         <v>23.6</v>
       </c>
       <c r="V19" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W19" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
         <v>5.6</v>
@@ -3827,19 +3894,19 @@
         <v>23.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.8</v>
+        <v>106.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
@@ -3854,19 +3921,19 @@
         <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
         <v>17</v>
       </c>
       <c r="AM19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
       </c>
       <c r="AO19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3875,10 +3942,10 @@
         <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -3887,7 +3954,7 @@
         <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW19" t="n">
         <v>4</v>
@@ -3908,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>18</v>
@@ -4033,10 +4100,10 @@
         <v>14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4051,13 +4118,13 @@
         <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4066,7 +4133,7 @@
         <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
         <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>0.419</v>
+        <v>0.411</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J21" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L21" t="n">
         <v>9.1</v>
@@ -4155,10 +4222,10 @@
         <v>15.2</v>
       </c>
       <c r="P21" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
@@ -4170,7 +4237,7 @@
         <v>40.7</v>
       </c>
       <c r="U21" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V21" t="n">
         <v>13</v>
@@ -4191,16 +4258,16 @@
         <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
         <v>21</v>
@@ -4209,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
@@ -4218,7 +4285,7 @@
         <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>6</v>
@@ -4239,7 +4306,7 @@
         <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4260,16 +4327,16 @@
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA21" t="n">
         <v>24</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
         <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>0.74</v>
+        <v>0.736</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J22" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L22" t="n">
         <v>8.1</v>
@@ -4331,7 +4398,7 @@
         <v>22.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="O22" t="n">
         <v>19.9</v>
@@ -4340,10 +4407,10 @@
         <v>24.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.804</v>
+        <v>0.803</v>
       </c>
       <c r="R22" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S22" t="n">
         <v>34.3</v>
@@ -4373,13 +4440,13 @@
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.2</v>
+        <v>106</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,13 +4458,13 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
@@ -4421,13 +4488,13 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -4436,13 +4503,13 @@
         <v>27</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23" t="n">
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="H23" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
@@ -4516,28 +4583,28 @@
         <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R23" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
         <v>7.6</v>
@@ -4555,13 +4622,13 @@
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4579,10 +4646,10 @@
         <v>21</v>
       </c>
       <c r="AJ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4615,10 +4682,10 @@
         <v>22</v>
       </c>
       <c r="AV23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW23" t="n">
         <v>14</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E25" t="n">
         <v>44</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.595</v>
+        <v>0.603</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L25" t="n">
         <v>9.5</v>
       </c>
       <c r="M25" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O25" t="n">
         <v>18.6</v>
@@ -4907,7 +4974,7 @@
         <v>8.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
@@ -4919,13 +4986,13 @@
         <v>21.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.4</v>
+        <v>105.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4937,16 +5004,16 @@
         <v>9</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>11</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
         <v>2</v>
@@ -4955,7 +5022,7 @@
         <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
@@ -4982,10 +5049,10 @@
         <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F26" t="n">
         <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.64</v>
+        <v>0.635</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,37 +5114,37 @@
         <v>39</v>
       </c>
       <c r="J26" t="n">
-        <v>86.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L26" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M26" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="N26" t="n">
         <v>0.372</v>
       </c>
       <c r="O26" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P26" t="n">
         <v>23.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.819</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S26" t="n">
         <v>33.7</v>
       </c>
       <c r="T26" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="U26" t="n">
         <v>23</v>
@@ -5089,7 +5156,7 @@
         <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
         <v>3.7</v>
@@ -5104,7 +5171,7 @@
         <v>106.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
@@ -5128,10 +5195,10 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
         <v>3</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5158,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
@@ -5176,7 +5243,7 @@
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5355,7 +5422,7 @@
         <v>23</v>
       </c>
       <c r="AZ27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5510,7 +5577,7 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR28" t="n">
         <v>27</v>
@@ -5531,7 +5598,7 @@
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F29" t="n">
         <v>31</v>
       </c>
       <c r="G29" t="n">
-        <v>0.575</v>
+        <v>0.569</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
@@ -5593,7 +5660,7 @@
         <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.443</v>
@@ -5602,31 +5669,31 @@
         <v>8.4</v>
       </c>
       <c r="M29" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="N29" t="n">
         <v>0.367</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
         <v>24.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="R29" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S29" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T29" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U29" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V29" t="n">
         <v>14.2</v>
@@ -5641,19 +5708,19 @@
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC29" t="n">
         <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5671,19 +5738,19 @@
         <v>23</v>
       </c>
       <c r="AJ29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK29" t="n">
         <v>21</v>
       </c>
-      <c r="AK29" t="n">
-        <v>22</v>
-      </c>
       <c r="AL29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN29" t="n">
         <v>12</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>13</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
@@ -5692,7 +5759,7 @@
         <v>7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
         <v>12</v>
@@ -5701,10 +5768,10 @@
         <v>19</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5713,22 +5780,22 @@
         <v>23</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" t="n">
         <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G30" t="n">
-        <v>0.311</v>
+        <v>0.315</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5775,7 +5842,7 @@
         <v>35.7</v>
       </c>
       <c r="J30" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.442</v>
@@ -5787,7 +5854,7 @@
         <v>19.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O30" t="n">
         <v>16.3</v>
@@ -5799,13 +5866,13 @@
         <v>0.746</v>
       </c>
       <c r="R30" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S30" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T30" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
@@ -5814,28 +5881,28 @@
         <v>14.7</v>
       </c>
       <c r="W30" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X30" t="n">
         <v>4.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-7</v>
+        <v>-6.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5847,7 +5914,7 @@
         <v>27</v>
       </c>
       <c r="AH30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI30" t="n">
         <v>28</v>
@@ -5868,13 +5935,13 @@
         <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP30" t="n">
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR30" t="n">
         <v>20</v>
@@ -5889,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="AV30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
@@ -5898,13 +5965,13 @@
         <v>20</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF31" t="n">
         <v>15</v>
@@ -6059,7 +6126,7 @@
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
         <v>17</v>
@@ -6074,7 +6141,7 @@
         <v>15</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-30-2013-14</t>
+          <t>2014-03-30</t>
         </is>
       </c>
     </row>
